--- a/Experiment: C1/data/terminal_velocity_analysis_bigger_bead.xlsx
+++ b/Experiment: C1/data/terminal_velocity_analysis_bigger_bead.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Lab C1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0353A629-7DC1-426D-A11C-DDF311DB7262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B4E46C-7C45-44C5-966D-97A760497D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{22961389-814C-44D6-A075-B6B4D851FF78}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +92,20 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -107,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -187,11 +201,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4472C4"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF4472C4"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF4472C4"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -221,6 +250,15 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -683,8 +721,8 @@
       <c r="H3" s="6">
         <v>2.81833</v>
       </c>
-      <c r="I3" s="6">
-        <v>0.30275000000000002</v>
+      <c r="I3" s="11">
+        <v>0.1236</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -712,8 +750,8 @@
       <c r="H4" s="8">
         <v>5.41167</v>
       </c>
-      <c r="I4" s="8">
-        <v>0.44413999999999998</v>
+      <c r="I4" s="12">
+        <v>0.18132000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -741,8 +779,8 @@
       <c r="H5" s="6">
         <v>8.1083300000000005</v>
       </c>
-      <c r="I5" s="6">
-        <v>0.51588000000000001</v>
+      <c r="I5" s="13">
+        <v>0.21062</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -770,8 +808,8 @@
       <c r="H6" s="8">
         <v>10.69167</v>
       </c>
-      <c r="I6" s="8">
-        <v>0.70386000000000004</v>
+      <c r="I6" s="12">
+        <v>0.28736</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -799,8 +837,8 @@
       <c r="H7" s="6">
         <v>13.30833</v>
       </c>
-      <c r="I7" s="6">
-        <v>0.84846999999999995</v>
+      <c r="I7" s="13">
+        <v>0.34638000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -828,8 +866,8 @@
       <c r="H8" s="8">
         <v>15.76667</v>
       </c>
-      <c r="I8" s="8">
-        <v>0.77368000000000003</v>
+      <c r="I8" s="12">
+        <v>0.31585999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -857,8 +895,8 @@
       <c r="H9" s="6">
         <v>18.28</v>
       </c>
-      <c r="I9" s="6">
-        <v>0.80845999999999996</v>
+      <c r="I9" s="13">
+        <v>0.32965</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -886,8 +924,8 @@
       <c r="H10" s="8">
         <v>20.83333</v>
       </c>
-      <c r="I10" s="8">
-        <v>0.96918000000000004</v>
+      <c r="I10" s="12">
+        <v>0.39567000000000002</v>
       </c>
     </row>
   </sheetData>
